--- a/output/pdf_financials_xlsx/HR.UN.xlsx
+++ b/output/pdf_financials_xlsx/HR.UN.xlsx
@@ -431,6 +431,15 @@
   </sheetPr>
   <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/HR.UN.xlsx
+++ b/output/pdf_financials_xlsx/HR.UN.xlsx
@@ -699,22 +699,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>15.036</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>33.399</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>14.793</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>13.849</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>11.577</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>14.498</v>
       </c>
     </row>
     <row r="13">
@@ -724,22 +724,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -824,22 +824,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-35.38</v>
+        <v>35.38</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>53.741</v>
+        <v>-53.741</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>101.437</v>
+        <v>-101.437</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-30.543</v>
+        <v>30.543</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-59.213</v>
+        <v>59.213</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-182.618</v>
+        <v>182.618</v>
       </c>
     </row>
     <row r="18">
@@ -1134,22 +1134,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>375.669</v>
+        <v>360.633</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-678.3</v>
+        <v>-711.699</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>946.26</v>
+        <v>931.467</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>31.147</v>
+        <v>17.298</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-178.927</v>
+        <v>-190.504</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-974.182</v>
+        <v>-988.6799999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1184,22 +1184,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>375.669</v>
+        <v>360.633</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-678.3</v>
+        <v>-711.699</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>946.26</v>
+        <v>931.467</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>31.147</v>
+        <v>17.298</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-178.927</v>
+        <v>-190.504</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-974.182</v>
+        <v>-988.6799999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3471,25 +3471,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>844.823</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>61.69</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-119.714</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>-791.564</v>
       </c>
     </row>
     <row r="100">
@@ -3508,25 +3500,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -3545,25 +3529,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3582,25 +3558,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3619,25 +3587,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3656,25 +3616,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3693,25 +3645,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>118.608</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3730,25 +3674,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D106" s="3" t="n">
+        <v>118.608</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3767,25 +3703,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3804,25 +3732,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3841,25 +3761,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3878,25 +3790,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3915,25 +3819,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3952,25 +3848,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3989,25 +3877,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -4026,25 +3906,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -4063,25 +3935,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -4100,25 +3964,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4137,25 +3993,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4174,25 +4022,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -4248,25 +4088,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -4285,25 +4117,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -4322,25 +4146,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -4359,25 +4175,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -4396,25 +4204,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -4433,25 +4233,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -4470,25 +4262,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -4544,25 +4328,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -4618,25 +4394,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>124.141</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>76.887</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>64.111</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>100.354</v>
       </c>
     </row>
     <row r="131">
@@ -4655,25 +4423,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4692,25 +4452,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>-47.254</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-12.776</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>36.243</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>-48.217</v>
       </c>
     </row>
     <row r="133">
@@ -4729,25 +4481,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>76.887</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>64.111</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>100.354</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>52.137</v>
       </c>
     </row>
     <row r="134">
@@ -4766,25 +4510,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>-35.582</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>-41.168</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>-39.588</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>-41.995</v>
       </c>
     </row>
     <row r="135">
@@ -4835,7 +4571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5585,16 +5321,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rentals from investment properties 15</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -5605,29 +5349,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n">
-        <v>834.64</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>847.146</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>816.99</v>
+        <v>-119.714</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>815.128</v>
+        <v>-791.564</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Property operating costs</t>
+          <t>Finance cost - operations 16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -5642,33 +5394,37 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-299.691</v>
+        <v>220.262</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-300.542</v>
+        <v>218.152</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-297.072</v>
+        <v>246.829</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-306.045</v>
+        <v>205.551</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Net operating income</t>
+          <t>Interest paid</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>InterestPaidSupplementalData</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5682,28 +5438,32 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>534.949</v>
+        <v>-171.242</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>546.604</v>
+        <v>-169.726</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>519.918</v>
+        <v>-152.813</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>509.083</v>
+        <v>-157.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Net income (loss) from equity accounted investments 4</t>
+          <t>Rental income accrued from the Bow and 100 Wynford 10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -5717,33 +5477,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="5" t="n">
+        <v>-86.55500000000001</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-92.92</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>2.477</v>
+        <v>-93.736</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-271.064</v>
+        <v>-94.559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finance cost - operations 16</t>
+          <t>Net (income) loss from equity accounted investments 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -5757,29 +5517,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n">
-        <v>-220.262</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>-218.152</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-246.829</v>
+        <v>-2.477</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-205.551</v>
+        <v>271.064</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finance income 16</t>
+          <t>Rent amortization of tenant inducements 15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -5794,28 +5562,32 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>14.793</v>
+        <v>4.691</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>13.849</v>
+        <v>4.514</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>11.577</v>
+        <v>4.574</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>14.498</v>
+        <v>4.508</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Trust expenses, net</t>
+          <t>Fair value adjustment on real estate assets 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -5829,33 +5601,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G23" s="5" t="n">
+        <v>-546.081</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>486.104</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-20.58</v>
+        <v>425.884</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-19.381</v>
+        <v>969.275</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fair value adjustment on financial instruments 16</t>
+          <t>Loss on sale of real estate assets, net of related costs 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -5869,29 +5641,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n">
-        <v>38.349</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>30.555</v>
+        <v>7.247</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>-8.452</v>
+        <v>11.154</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-17.498</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fair value adjustment on real estate assets 3</t>
+          <t>Fair value adjustment on financial instruments 16</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -5906,28 +5684,32 @@
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>546.081</v>
+        <v>-38.349</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>-486.104</v>
+        <v>-30.555</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>-425.884</v>
+        <v>8.452</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>-969.275</v>
+        <v>17.498</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loss on sale of real estate assets, net of related costs 3</t>
+          <t>Unit-based compensation expense 13(b)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -5941,31 +5723,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G26" s="5" t="n">
+        <v>6.765</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>-7.247</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>-11.154</v>
+        <v>3.906</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-2.254</v>
+        <v>9.914</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Transaction costs 18</t>
+          <t>Deferred income tax recovery 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -5989,32 +5773,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="5" t="n">
+        <v>-60.675</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>-12.74</v>
+        <v>-184.269</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Net loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Change in other non-cash operating items 17</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -6025,33 +5807,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G28" s="5" t="n">
+        <v>-24.897</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-12.161</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-178.927</v>
+        <v>2.686</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-974.182</v>
+        <v>-63.582</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Income tax recovery 24</t>
+          <t>Items not affecting cash total</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -6065,40 +5847,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G29" s="5" t="n">
+        <v>255.054</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>294.625</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>59.213</v>
+        <v>274.07</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>182.618</v>
+        <v>188.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Properties under development</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Acquisitions 3, 17</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -6114,32 +5892,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H30" s="5" t="n">
+        <v>-18.666</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-119.714</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>-791.564</v>
+        <v>-104.468</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Properties under development</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Items that are or may be reclassified subsequently to net loss 14</t>
+          <t>Additions 3, 17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -6153,37 +5931,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G31" s="5" t="n">
+        <v>-70.024</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>-162.273</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>393.292</v>
+        <v>-159.57</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>-219.573</v>
+        <v>-34.688</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Properties under development</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Total comprehensive income (loss) attributable to unitholders</t>
+          <t>Net proceeds on disposition of properties under development</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -6197,33 +5971,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n">
-        <v>1166.393</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>-69.512</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>273.578</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>-1011.137</v>
+        <v>22.089</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Unitholders' equity, January 1, 2024 $5,219,408 $6,778,212 ($7,131,874)</t>
+          <t>Net proceeds on disposition of investment properties</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -6242,32 +6022,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H33" s="5" t="n">
+        <v>371.9</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>5192.375</v>
+        <v>330.94</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>326.629</v>
+        <v>101.948</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Issuance of Units 1,413 — —</t>
+          <t>Redevelopment 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -6287,34 +6065,36 @@
         </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>1.413</v>
+        <v>-7.203</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-22.403</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>-19.323</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Net loss — (119,714) —</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Capital expenditures 3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -6325,37 +6105,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G35" s="5" t="n">
+        <v>-35.582</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-119.714</v>
+        <v>-41.168</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-119.714</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-39.588</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>-41.995</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Distributions to unitholders 13 — — (188,623)</t>
+          <t>Leasing expenses and tenant inducements 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -6369,37 +6145,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G36" s="5" t="n">
+        <v>-8.516</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>-188.623</v>
+        <v>-4.747</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>-188.623</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.629</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-1.938</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Distributions in Units 13 157,209 — (157,209)</t>
+          <t>Contributions to equity accounted investments</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -6418,36 +6190,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H37" s="5" t="n">
+        <v>-36.988</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>-25.432</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>-30.146</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Other comprehensive income — — —</t>
+          <t>Distributions received from equity accounted investments</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -6466,32 +6232,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H38" s="5" t="n">
+        <v>44.398</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>393.292</v>
+        <v>49.738</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>393.292</v>
+        <v>49.511</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2024 5,378,030 6,658,498 (7,477,706)</t>
+          <t>Advances of mortgages receivable 6</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -6510,32 +6274,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H39" s="5" t="n">
+        <v>-16.008</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>5278.743</v>
+        <v>-36.004</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>719.921</v>
+        <v>-102.398</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Issuance of Units 25,751 — —</t>
+          <t>Repayments of mortgages receivable 6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -6554,34 +6316,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H40" s="5" t="n">
+        <v>52.864</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>25.751</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>80.64100000000001</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>17.045</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net loss — (791,564) —</t>
+          <t>Restricted cash 6</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -6595,39 +6353,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G41" s="5" t="n">
+        <v>-17.909</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>-69.181</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>-791.564</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>83.83799999999999</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>2.799</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Distributions to unitholders 13 — — (157,639)</t>
+          <t>Investment properties total</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -6641,39 +6393,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G42" s="5" t="n">
+        <v>225.954</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>112.862</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-157.639</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>173.152</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>-59.185</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Distributions in Units 13 39,684 — (39,684)</t>
+          <t>Lines of credit 8</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -6692,36 +6438,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H43" s="5" t="n">
+        <v>292.21</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>31.444</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>538.213</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Other comprehensive loss 14 — — —</t>
+          <t>Advances 8</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -6735,33 +6475,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n">
-        <v>-131.202</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>-131.202</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-219.573</v>
+        <v>2.283</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-219.573</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2025 5,443,465 5,866,934 (7,675,029)</t>
+          <t>Principal repayments 8</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -6775,33 +6519,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G45" s="5" t="n">
+        <v>-301.132</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>-144.534</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>4135.718</v>
+        <v>-160.146</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>500.348</v>
+        <v>-127.545</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mortgages payable</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Net income from equity accounted investments 4</t>
+          <t>Redemption of debentures payable 8</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -6815,31 +6559,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n">
-        <v>47.139</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>145.459</v>
+        <v>-250</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>2.477</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-350</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>-400</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mortgages payable</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gain on disposal of purchase option</t>
+          <t>Proceeds from issuance of debentures payable, net 8</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -6858,13 +6606,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H47" s="5" t="n">
-        <v>30.568</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>248.8</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -6875,13 +6623,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mortgages payable</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trust expenses</t>
+          <t>Cash distributions paid to unitholders 17</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -6895,38 +6647,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G48" s="5" t="n">
-        <v>-22.121</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>-24.385</v>
+        <v>-170.564</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>-20.58</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-183.36</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-188.954</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mortgages payable</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Net income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Mortgages payable total</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -6937,36 +6689,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G49" s="5" t="n">
+        <v>-528.2619999999999</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>31.147</v>
+        <v>-420.263</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>-178.927</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-410.979</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>-177.462</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Mortgages payable</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Income tax recovery 22</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Increase (decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -6983,32 +6739,34 @@
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>30.543</v>
+        <v>-12.776</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>59.213</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>36.243</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>-48.217</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mortgages payable</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
+          <t>Cash and cash equivalents, beginning of year 7</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7021,42 +6779,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G51" s="5" t="n">
+        <v>124.141</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>61.69</v>
+        <v>76.887</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>-119.714</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>64.111</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>100.354</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Items that are or may be reclassified subsequently to net income (loss) 14</t>
+          <t>Cash and cash equivalents, end of year 7</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7069,37 +6823,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G52" s="5" t="n">
+        <v>76.887</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>-131.202</v>
+        <v>64.111</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>393.292</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>100.354</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>52.137</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Unitholders' equity, January 1, 2023 $5,124,265 $6,716,522 ($6,811,331)</t>
+          <t>Net income (loss)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -7119,10 +6869,10 @@
         </is>
       </c>
       <c r="H53" s="5" t="n">
-        <v>5487.287</v>
+        <v>61.69</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>457.831</v>
+        <v>-119.714</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -7133,17 +6883,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Issuance of Units 1,695 — —</t>
+          <t>Net income from equity accounted investments 4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -7157,18 +6907,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G54" s="5" t="n">
+        <v>-47.139</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-145.459</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>-2.477</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -7179,17 +6925,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Net income — 61,690 —</t>
+          <t>Deferred income tax recovery 22</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -7203,16 +6949,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G55" s="5" t="n">
-        <v>61.69</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>61.69</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-32.345</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>-60.675</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -7223,17 +6969,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Distributions to unitholders 13 — — (184,372)</t>
+          <t>Acquisitions 3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -7247,13 +6993,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G56" s="5" t="n">
+        <v>-78.44799999999999</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>-184.372</v>
+        <v>-0.066</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -7269,17 +7013,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Distributions in Units 13 136,171 — (136,171)</t>
+          <t>Unsecured term loans 8</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -7293,15 +7037,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G57" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>-125</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -7317,17 +7057,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Units repurchased and cancelled 13(d) (42,723) — —</t>
+          <t>New mortgages payable 8</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -7341,11 +7081,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n">
-        <v>-42.723</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>-42.723</v>
+        <v>20.361</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -7361,17 +7103,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2023 5,219,408 6,778,212 (7,131,874)</t>
+          <t>Net advances 8</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -7390,11 +7132,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H59" s="5" t="n">
-        <v>5192.375</v>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I59" s="5" t="n">
-        <v>326.629</v>
+        <v>2.283</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -7405,17 +7149,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Other comprehensive income 14 — — —</t>
+          <t>Proceeds from issuance of Units</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -7429,14 +7173,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n">
-        <v>321.57</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>393.292</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>393.292</v>
+        <v>-0.013</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -7447,17 +7195,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2024 $5,378,030 $6,658,498 ($7,477,706)</t>
+          <t>Units repurchased and cancelled 13(d)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -7471,16 +7219,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G61" s="5" t="n">
+        <v>-297.056</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>5278.743</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>719.921</v>
+        <v>-42.723</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -7491,16 +7239,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Proceeds on disposal of purchase option 6</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -7511,13 +7267,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="5" t="n">
+        <v>844.823</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>30.568</v>
+        <v>61.69</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -7533,13 +7287,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of real estate assets, net of related costs 3</t>
+          <t>(Gain) loss on sale of real estate assets, net of related costs 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -7554,10 +7312,10 @@
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>7.332</v>
+        <v>-7.332</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>-7.247</v>
+        <v>7.247</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -7573,20 +7331,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Net income before income taxes</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Deferred income tax expense (recovery) 22</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -7598,10 +7356,10 @@
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>946.26</v>
+        <v>100.108</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>31.147</v>
+        <v>-32.345</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -7617,13 +7375,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Properties under development</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense) 22</t>
+          <t>Acquisitions 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -7638,10 +7400,10 @@
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-101.437</v>
+        <v>-90.845</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>30.543</v>
+        <v>-18.666</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -7657,18 +7419,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Investment properties</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t>Deferred revenue 10</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ChangeInOtherWorkingCapital</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7682,10 +7448,12 @@
         </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>844.823</v>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>61.69</v>
+        <v>118.608</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -7701,17 +7469,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Items that are or may be reclassified subsequently to net income 14</t>
+          <t>Net proceeds on disposition of real estate assets</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -7726,10 +7494,10 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>321.57</v>
+        <v>263.679</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>-131.202</v>
+        <v>371.9</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -7745,17 +7513,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Unitholders' equity, January 1, 2022 $5,417,419 $5,871,699 ($6,651,546)</t>
+          <t>Redevelopment, net of insurance proceeds 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -7770,10 +7538,10 @@
         </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>4773.833</v>
+        <v>5.425</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>136.261</v>
+        <v>-7.203</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -7789,17 +7557,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of Units 3,902 — —</t>
+          <t>Equity accounted investments, net</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -7814,12 +7582,10 @@
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>3.902</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>57.559</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>7.41</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -7835,17 +7601,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Net income — 844,823 —</t>
+          <t>Mortgages receivable, net</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -7860,12 +7626,10 @@
         </is>
       </c>
       <c r="G70" s="5" t="n">
-        <v>844.823</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>32.732</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>36.856</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -7881,17 +7645,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Distributions to unitholders — — (159,785)</t>
+          <t>Proceeds from sale of Primaris REIT units</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -7906,7 +7670,7 @@
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-159.785</v>
+        <v>49.275</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -7927,17 +7691,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Units repurchased and cancelled 13(d) (297,056) — —</t>
+          <t>Proceeds from issuance of Units 17</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -7952,12 +7716,10 @@
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-297.056</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.331</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>-0.013</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -7973,17 +7735,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2022 5,124,265 6,716,522 (6,811,331)</t>
+          <t>Distributions paid to unitholders 17</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -7998,10 +7760,10 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>5487.287</v>
+        <v>-179.743</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>457.831</v>
+        <v>-170.564</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -8017,20 +7779,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of Units 1,695 — —</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Decrease in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -8042,12 +7808,10 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-47.254</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>-12.776</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -8066,14 +7830,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Distributions to unitholders — — (184,372)</t>
+          <t>Rentals from investment properties 15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -8088,22 +7848,16 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-184.372</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>834.64</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>847.146</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>816.99</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>815.128</v>
       </c>
     </row>
     <row r="76">
@@ -8112,14 +7866,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2023 $5,083,237 $6,778,212 ($6,995,703)</t>
+          <t>Property operating costs</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -8134,20 +7884,16 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>5192.375</v>
+        <v>-299.691</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>326.629</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-300.542</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>-297.072</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>-306.045</v>
       </c>
     </row>
     <row r="77">
@@ -8156,42 +7902,38 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rentals from investment properties 14 $</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>1149.45</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>1098.68</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>534.949</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>546.604</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>519.918</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>509.083</v>
       </c>
     </row>
     <row r="78">
@@ -8200,22 +7942,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Property operating costs</t>
+          <t>Net income (loss) from equity accounted investments 4</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>-438.475</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>-435.014</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -8227,15 +7969,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="5" t="n">
+        <v>2.477</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>-271.064</v>
       </c>
     </row>
     <row r="79">
@@ -8244,42 +7982,34 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Property operating income total</t>
+          <t>Finance cost - operations 16</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>710.975</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>663.6660000000001</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>-220.262</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>-218.152</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>-246.829</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>-205.551</v>
       </c>
     </row>
     <row r="80">
@@ -8288,42 +8018,38 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Net income (loss) from equity accounted investments 4</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>31.201</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>-16.986</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Finance income 16</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>14.793</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>13.849</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>11.577</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>14.498</v>
       </c>
     </row>
     <row r="81">
@@ -8332,22 +8058,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Finance cost - operations 15</t>
+          <t>Trust expenses, net</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>-256.496</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>-228.869</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -8359,15 +8085,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="5" t="n">
+        <v>-20.58</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>-19.381</v>
       </c>
     </row>
     <row r="82">
@@ -8376,42 +8098,34 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Finance income 15</t>
+          <t>Fair value adjustment on financial instruments 16</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>15.036</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>33.399</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>38.349</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>30.555</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>-8.452</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>-17.498</v>
       </c>
     </row>
     <row r="83">
@@ -8420,42 +8134,34 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Trust expenses</t>
+          <t>Fair value adjustment on real estate assets 3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>-27.293</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>-14.297</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>546.081</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>-486.104</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>-425.884</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>-969.275</v>
       </c>
     </row>
     <row r="84">
@@ -8464,42 +8170,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fair value adjustment on financial instruments 15</t>
+          <t>Loss on sale of real estate assets, net of related costs 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>-19.483</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>82.974</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H84" s="5" t="n">
+        <v>-7.247</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>-11.154</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>-2.254</v>
       </c>
     </row>
     <row r="85">
@@ -8508,22 +8208,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fair value adjustment on real estate assets 3</t>
+          <t>Transaction costs 18</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" s="5" t="n">
-        <v>-103.903</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>-1195.958</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -8540,10 +8240,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J85" s="5" t="n">
+        <v>-12.74</v>
       </c>
     </row>
     <row r="86">
@@ -8552,22 +8250,26 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of real estate assets, net of related costs 3</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>25.632</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>-2.229</v>
+          <t>Net loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -8579,15 +8281,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I86" s="5" t="n">
+        <v>-178.927</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>-974.182</v>
       </c>
     </row>
     <row r="87">
@@ -8596,26 +8294,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Net income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>375.669</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>-678.3</v>
+          <t>Income tax recovery 24</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -8627,15 +8321,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="5" t="n">
+        <v>59.213</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>182.618</v>
       </c>
     </row>
     <row r="88">
@@ -8644,26 +8334,26 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Income tax (expense) recovery 21</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>-35.38</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>53.741</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -8675,15 +8365,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I88" s="5" t="n">
+        <v>-119.714</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>-791.564</v>
       </c>
     </row>
     <row r="89">
@@ -8694,24 +8380,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>340.289</v>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>-624.559</v>
+          <t>Items that are or may be reclassified subsequently to net loss 14</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -8723,15 +8409,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="5" t="n">
+        <v>393.292</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-219.573</v>
       </c>
     </row>
     <row r="90">
@@ -8742,44 +8424,36 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Items that are or may be reclassified subsequently to net income (loss) 13</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>-125.326</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>-86.66200000000001</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total comprehensive income (loss) attributable to unitholders</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>1166.393</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>-69.512</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>273.578</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>-1011.137</v>
       </c>
     </row>
     <row r="91">
@@ -8790,20 +8464,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Total comprehensive income (loss) attributable to unitholders $</t>
+          <t>Unitholders' equity, January 1, 2024 $5,219,408 $6,778,212 ($7,131,874)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" s="5" t="n">
-        <v>214.963</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>-711.221</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -8815,15 +8493,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="5" t="n">
+        <v>5192.375</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>326.629</v>
       </c>
     </row>
     <row r="92">
@@ -8834,35 +8508,35 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Unitholders' equity, January 1, 2019 $ 5,366,464 $ 5,558,062 $ (4,096,250) $</t>
+          <t>Issuance of Units 1,413 — —</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" s="5" t="n">
-        <v>7200.1</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>371.824</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H92" s="5" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>1.413</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -8878,17 +8552,19 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of Units 23,035 - -</t>
+          <t>Net loss — (119,714) —</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" s="5" t="n">
-        <v>23.035</v>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8900,15 +8576,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H93" s="5" t="n">
+        <v>-119.714</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>-119.714</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -8924,17 +8596,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Net income - 340,289 -</t>
+          <t>Distributions to unitholders 13 — — (188,623)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" s="5" t="n">
-        <v>340.289</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8946,15 +8620,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H94" s="5" t="n">
+        <v>-188.623</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>-188.623</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -8970,17 +8640,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Distributions to unitholders - - (394,181)</t>
+          <t>Distributions in Units 13 157,209 — (157,209)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" s="5" t="n">
-        <v>-394.181</v>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9016,20 +8688,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Other comprehensive loss 13 - - -</t>
+          <t>Other comprehensive income — — —</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" s="5" t="n">
-        <v>-125.326</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>-125.326</v>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -9041,15 +8717,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" s="5" t="n">
+        <v>393.292</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>393.292</v>
       </c>
     </row>
     <row r="97">
@@ -9060,20 +8732,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2019 5,389,499 5,898,351 (4,490,431)</t>
+          <t>Unitholders' equity, December 31, 2024 5,378,030 6,658,498 (7,477,706)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="n">
-        <v>7043.917</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>246.498</v>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -9085,15 +8761,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="5" t="n">
+        <v>5278.743</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>719.921</v>
       </c>
     </row>
     <row r="98">
@@ -9104,17 +8776,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of Units 2,267 - -</t>
+          <t>Issuance of Units 25,751 — —</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" s="5" t="n">
-        <v>2.267</v>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9131,10 +8805,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I98" s="5" t="n">
+        <v>25.751</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -9150,17 +8822,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Net loss - (624,559) -</t>
+          <t>Net loss — (791,564) —</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" s="5" t="n">
-        <v>-624.559</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9177,10 +8851,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="5" t="n">
+        <v>-791.564</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -9196,17 +8868,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Distributions to unitholders - - (263,572)</t>
+          <t>Distributions to unitholders 13 — — (157,639)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" s="5" t="n">
-        <v>-263.572</v>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9223,10 +8897,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I100" s="5" t="n">
+        <v>-157.639</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -9242,37 +8914,2615 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Distributions in Units 13 39,684 — (39,684)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss 14 — — —</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-131.202</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>-131.202</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>-219.573</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>-219.573</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, December 31, 2025 5,443,465 5,866,934 (7,675,029)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>4135.718</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>500.348</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Net income from equity accounted investments 4</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>47.139</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>145.459</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>2.477</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Gain on disposal of purchase option</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>30.568</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Trust expenses</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>-22.121</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>-24.385</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>-20.58</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Net income (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>31.147</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>-178.927</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Income tax recovery 22</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>30.543</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>59.213</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Net income (loss)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>61.69</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>-119.714</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Items that are or may be reclassified subsequently to net income (loss) 14</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>-131.202</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>393.292</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, January 1, 2023 $5,124,265 $6,716,522 ($6,811,331)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>5487.287</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>457.831</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Issuance of Units 1,695 — —</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Net income — 61,690 —</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>61.69</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>61.69</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders 13 — — (184,372)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>-184.372</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Distributions in Units 13 136,171 — (136,171)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Units repurchased and cancelled 13(d) (42,723) — —</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>-42.723</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>-42.723</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, December 31, 2023 5,219,408 6,778,212 (7,131,874)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>5192.375</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>326.629</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Other comprehensive income 14 — — —</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>393.292</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>393.292</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, December 31, 2024 $5,378,030 $6,658,498 ($7,477,706)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>5278.743</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>719.921</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Proceeds on disposal of purchase option 6</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>30.568</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Gain (loss) on sale of real estate assets, net of related costs 3</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>7.332</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>-7.247</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Net income before income taxes</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>946.26</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>31.147</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Income tax recovery (expense) 22</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>-101.437</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>30.543</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>844.823</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>61.69</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Items that are or may be reclassified subsequently to net income 14</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>-131.202</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, January 1, 2022 $5,417,419 $5,871,699 ($6,651,546)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>4773.833</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>136.261</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of Units 3,902 — —</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>3.902</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Net income — 844,823 —</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>844.823</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders — — (159,785)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>-159.785</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Units repurchased and cancelled 13(d) (297,056) — —</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>-297.056</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, December 31, 2022 5,124,265 6,716,522 (6,811,331)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>5487.287</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>457.831</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of Units 1,695 — —</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders — — (184,372)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>-184.372</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, December 31, 2023 $5,083,237 $6,778,212 ($6,995,703)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>5192.375</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>326.629</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Rentals from investment properties 14 $</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>1149.45</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>1098.68</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Property operating costs</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" s="5" t="n">
+        <v>-438.475</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>-435.014</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Property operating income total</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" s="5" t="n">
+        <v>710.975</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>663.6660000000001</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Net income (loss) from equity accounted investments 4</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" s="5" t="n">
+        <v>31.201</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-16.986</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Finance cost - operations 15</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>-256.496</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>-228.869</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Finance income 15</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>15.036</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>33.399</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Trust expenses</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" s="5" t="n">
+        <v>-27.293</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>-14.297</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Fair value adjustment on financial instruments 15</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
+        <v>-19.483</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>82.974</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Fair value adjustment on real estate assets 3</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" s="5" t="n">
+        <v>-103.903</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>-1195.958</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Gain (loss) on sale of real estate assets, net of related costs 3</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" s="5" t="n">
+        <v>25.632</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>-2.229</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Net income (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>375.669</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>-678.3</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Income tax (expense) recovery 21</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>-35.38</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>53.741</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Property operating income</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Net income (loss)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>340.289</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>-624.559</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Items that are or may be reclassified subsequently to net income (loss) 13</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>-125.326</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>-86.66200000000001</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Total comprehensive income (loss) attributable to unitholders $</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" s="5" t="n">
+        <v>214.963</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>-711.221</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
           <t>Value of Accumulated Accumulated comprehensive</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, January 1, 2019 $ 5,366,464 $ 5,558,062 $ (4,096,250) $</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" s="5" t="n">
+        <v>7200.1</v>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>371.824</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of Units 23,035 - -</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" s="5" t="n">
+        <v>23.035</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Net income - 340,289 -</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" s="5" t="n">
+        <v>340.289</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders - - (394,181)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" s="5" t="n">
+        <v>-394.181</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss 13 - - -</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" s="5" t="n">
+        <v>-125.326</v>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>-125.326</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, December 31, 2019 5,389,499 5,898,351 (4,490,431)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" s="5" t="n">
+        <v>7043.917</v>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>246.498</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of Units 2,267 - -</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" s="5" t="n">
+        <v>2.267</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Net loss - (624,559) -</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" s="5" t="n">
+        <v>-624.559</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders - - (263,572)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" s="5" t="n">
+        <v>-263.572</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
         <is>
           <t>Unitholders' equity, December 31, 2020 $ 5,391,766 $ 5,273,792 $ (4,754,003) $</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" s="5" t="n">
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" s="5" t="n">
         <v>6071.391</v>
       </c>
-      <c r="F101" s="5" t="n">
+      <c r="F159" s="5" t="n">
         <v>159.836</v>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/HR.UN.xlsx
+++ b/output/pdf_financials_xlsx/HR.UN.xlsx
@@ -830,16 +830,16 @@
         <v>-53.741</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-101.437</v>
+        <v>101.437</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>30.543</v>
+        <v>-30.543</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>59.213</v>
+        <v>-59.213</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>182.618</v>
+        <v>-182.618</v>
       </c>
     </row>
     <row r="18">
@@ -1320,25 +1320,17 @@
       <c r="C34" s="3" t="n">
         <v>62.859</v>
       </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D34" s="3" t="n">
+        <v>76.887</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>64.111</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>100.354</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>52.137</v>
       </c>
     </row>
     <row r="35">
@@ -1353,25 +1345,17 @@
       <c r="C35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1386,25 +1370,17 @@
       <c r="C36" s="3" t="n">
         <v>62.859</v>
       </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D36" s="3" t="n">
+        <v>76.887</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>64.111</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>100.354</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>52.137</v>
       </c>
     </row>
     <row r="37">
@@ -1419,25 +1395,17 @@
       <c r="C37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1452,25 +1420,17 @@
       <c r="C38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1485,25 +1445,17 @@
       <c r="C39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1518,25 +1470,17 @@
       <c r="C40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1551,25 +1495,17 @@
       <c r="C41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1584,25 +1520,17 @@
       <c r="C42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1617,25 +1545,17 @@
       <c r="C43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1650,25 +1570,17 @@
       <c r="C44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1683,25 +1595,17 @@
       <c r="C45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1716,25 +1620,17 @@
       <c r="C46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1749,25 +1645,17 @@
       <c r="C47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1782,25 +1670,17 @@
       <c r="C48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1852,25 +1732,17 @@
       <c r="C50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1885,25 +1757,17 @@
       <c r="C51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1918,25 +1782,17 @@
       <c r="C52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1951,25 +1807,17 @@
       <c r="C53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1984,25 +1832,17 @@
       <c r="C54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2054,25 +1894,17 @@
       <c r="C56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2087,25 +1919,17 @@
       <c r="C57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2120,25 +1944,17 @@
       <c r="C58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2153,25 +1969,17 @@
       <c r="C59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2186,25 +1994,17 @@
       <c r="C60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2219,25 +2019,17 @@
       <c r="C61" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2289,25 +2081,17 @@
       <c r="C63" s="3" t="n">
         <v>11598.979</v>
       </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D63" s="3" t="n">
+        <v>9680.094999999999</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>8886.361999999999</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>9007.458000000001</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>7155.637</v>
       </c>
     </row>
     <row r="64">
@@ -2322,25 +2106,17 @@
       <c r="C64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2355,25 +2131,17 @@
       <c r="C65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2388,25 +2156,17 @@
       <c r="C66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2421,25 +2181,17 @@
       <c r="C67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2454,25 +2206,17 @@
       <c r="C68" s="3" t="n">
         <v>369.186</v>
       </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D68" s="3" t="n">
+        <v>309.505</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>335.606</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>304.978</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>237.789</v>
       </c>
     </row>
     <row r="69">
@@ -2487,25 +2231,17 @@
       <c r="C69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2520,25 +2256,17 @@
       <c r="C70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2553,25 +2281,17 @@
       <c r="C71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2586,25 +2306,17 @@
       <c r="C72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D72" s="3" t="n">
+        <v>986.2430000000001</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>947.671</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>906.3630000000001</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>862.139</v>
       </c>
     </row>
     <row r="73">
@@ -2619,25 +2331,17 @@
       <c r="C73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2652,25 +2356,17 @@
       <c r="C74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D74" s="3" t="n">
+        <v>986.2430000000001</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>947.671</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>906.3630000000001</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>862.139</v>
       </c>
     </row>
     <row r="75">
@@ -2685,25 +2381,17 @@
       <c r="C75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2755,25 +2443,17 @@
       <c r="C77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2788,25 +2468,17 @@
       <c r="C78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2821,25 +2493,17 @@
       <c r="C79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2891,25 +2555,17 @@
       <c r="C81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2924,25 +2580,17 @@
       <c r="C82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2957,25 +2605,17 @@
       <c r="C83" s="3" t="n">
         <v>348.755</v>
       </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D83" s="3" t="n">
+        <v>483.048</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>437.214</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>413.186</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>212.781</v>
       </c>
     </row>
     <row r="84">
@@ -2990,25 +2630,17 @@
       <c r="C84" s="3" t="n">
         <v>348.755</v>
       </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D84" s="3" t="n">
+        <v>483.048</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>437.214</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>413.186</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>212.781</v>
       </c>
     </row>
     <row r="85">
@@ -3023,25 +2655,17 @@
       <c r="C85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3093,25 +2717,17 @@
       <c r="C87" s="3" t="n">
         <v>7284.053</v>
       </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D87" s="3" t="n">
+        <v>5925.316</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>5585.268</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>5341.744</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>4972.568</v>
       </c>
     </row>
     <row r="88">
@@ -3126,25 +2742,17 @@
       <c r="C88" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3159,25 +2767,17 @@
       <c r="C89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -3229,25 +2829,17 @@
       <c r="C91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -3262,25 +2854,17 @@
       <c r="C92" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -3295,25 +2879,17 @@
       <c r="C93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -3328,25 +2904,17 @@
       <c r="C94" s="3" t="n">
         <v>4314.926</v>
       </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D94" s="3" t="n">
+        <v>3754.779</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>3301.094</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>3665.714</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>2183.069</v>
       </c>
     </row>
     <row r="95">
@@ -3361,25 +2929,17 @@
       <c r="C95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3394,25 +2954,17 @@
       <c r="C96" s="3" t="n">
         <v>4314.926</v>
       </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D96" s="3" t="n">
+        <v>3754.779</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>3301.094</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>3665.714</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>2183.069</v>
       </c>
     </row>
     <row r="97">
@@ -3427,25 +2979,17 @@
       <c r="C97" s="3" t="n">
         <v>0.3720091225270776</v>
       </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D97" s="3" t="n">
+        <v>0.3878865858237961</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0.3714786771009329</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0.4069643177908795</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0.3050838101485584</v>
       </c>
     </row>
     <row r="98">
@@ -4571,7 +4115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J159"/>
+  <dimension ref="A1:J170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4645,35 +4189,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Investment properties 3 $</t>
+          <t>Investment properties 3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="5" t="n">
-        <v>11988.347</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>11149.13</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>8799.316999999999</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>7811.543</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>7996.81</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>6370.453</v>
       </c>
     </row>
     <row r="3">
@@ -4699,25 +4239,17 @@
       <c r="F3" s="5" t="n">
         <v>449.849</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>880.778</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1074.819</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1010.648</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>785.184</v>
       </c>
     </row>
     <row r="4">
@@ -4747,25 +4279,17 @@
       <c r="F4" s="5" t="n">
         <v>11598.979</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G4" s="5" t="n">
+        <v>9680.094999999999</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>8886.361999999999</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>9007.458000000001</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>7155.637</v>
       </c>
     </row>
     <row r="5">
@@ -4791,25 +4315,17 @@
       <c r="F5" s="5" t="n">
         <v>955.468</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G5" s="5" t="n">
+        <v>1060.268</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1165.012</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1275.549</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>484.702</v>
       </c>
     </row>
     <row r="6">
@@ -4835,25 +4351,17 @@
       <c r="F6" s="5" t="n">
         <v>219.05</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G6" s="5" t="n">
+        <v>294.028</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>293.15</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1142.9</v>
       </c>
     </row>
     <row r="7">
@@ -4883,25 +4391,17 @@
       <c r="F7" s="5" t="n">
         <v>519.088</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G7" s="5" t="n">
+        <v>301.325</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>369.008</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>177.246</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>272.91</v>
       </c>
     </row>
     <row r="8">
@@ -4931,25 +4431,17 @@
       <c r="F8" s="5" t="n">
         <v>62.859</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G8" s="5" t="n">
+        <v>76.887</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>64.111</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>100.354</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>52.137</v>
       </c>
     </row>
     <row r="9">
@@ -4965,35 +4457,31 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Debt 8 $</t>
+          <t>Debt 8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" s="5" t="n">
-        <v>6375.86</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>6368.316</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>3922.529</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>3686.833</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>3537.384</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>3501.891</v>
       </c>
     </row>
     <row r="10">
@@ -5019,25 +4507,17 @@
       <c r="F10" s="5" t="n">
         <v>197.796</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G10" s="5" t="n">
+        <v>217.668</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>177.944</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>157.968</v>
       </c>
     </row>
     <row r="11">
@@ -5053,39 +4533,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deferred tax liability 21</t>
+          <t>Deferred revenue 10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NonCurrentDeferredTaxesLiabilities</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>409.381</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>348.755</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CurrentDeferredRevenue</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>986.2430000000001</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>947.671</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>906.3630000000001</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>862.139</v>
       </c>
     </row>
     <row r="12">
@@ -5101,19 +4577,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 10</t>
+          <t>Deferred tax liability 24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>281.595</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>369.186</v>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -5125,15 +4605,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="5" t="n">
+        <v>413.186</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>212.781</v>
       </c>
     </row>
     <row r="13">
@@ -5149,37 +4625,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liabilities classified as held for sale 5</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" s="5" t="n">
-        <v>49.416</v>
+          <t>Accounts payable and accrued liabilities 11</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G13" s="5" t="n">
+        <v>309.505</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>335.606</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>304.978</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>237.789</v>
       </c>
     </row>
     <row r="14">
@@ -5195,34 +4669,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liabilities total</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
+          <t>Liabilities classified as held for sale 5</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" s="5" t="n">
-        <v>7439.425</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>7284.053</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>49.416</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>6.323</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="5" t="n">
+        <v>13.033</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5243,35 +4711,31 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Unitholders' equity</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Liabilities total</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
-        <v>7043.917</v>
+        <v>7439.425</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>6071.391</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7284.053</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>5925.316</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>5585.268</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>5341.744</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>4972.568</v>
       </c>
     </row>
     <row r="16">
@@ -5282,63 +4746,51 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Subsequent events 24</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Subsequent events 24</t>
+          <t>Unitholders' equity</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="5" t="n">
-        <v>14483.342</v>
+        <v>7043.917</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>13355.444</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6071.391</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>5487.287</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>5192.375</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>5278.743</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>4135.718</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Commitments and contingencies                                     25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Subsequent events 4, 5, 8(c),</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -5360,26 +4812,26 @@
         </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-119.714</v>
+        <v>0.027</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-791.564</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Commitments and contingencies                                     25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finance cost - operations 16</t>
+          <t>Commitments and contingencies                                     25 total</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -5393,38 +4845,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>220.262</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>218.152</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I18" s="5" t="n">
-        <v>246.829</v>
+        <v>10620.487</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>205.551</v>
+        <v>9108.286</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Interest paid</t>
+          <t>Deferred tax liability 22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>InterestPaidSupplementalData</t>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5438,32 +4894,34 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-171.242</v>
+        <v>483.048</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-169.726</v>
+        <v>437.214</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-152.813</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>-157.66</v>
+        <v>413.186</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Subsequent events                                                      9, 13(b), 25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rental income accrued from the Bow and 100 Wynford 10</t>
+          <t>Subsequent events                                                      9, 13(b), 25 total</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -5477,33 +4935,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n">
-        <v>-86.55500000000001</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-92.92</v>
+        <v>10777.643</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-93.736</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>-94.559</v>
+        <v>10620.487</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Commitments and contingencies                                    23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Net (income) loss from equity accounted investments 4</t>
+          <t>Subsequent events 3, 8(b),</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -5517,37 +4979,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>-2.477</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>271.064</v>
+      <c r="G21" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Commitments and contingencies                                    23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rent amortization of tenant inducements 15</t>
+          <t>Commitments and contingencies                                    23 total</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -5562,206 +5024,228 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>4.691</v>
+        <v>11412.603</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>4.514</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>4.574</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>4.508</v>
+        <v>10777.643</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Real estate assets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fair value adjustment on real estate assets 3</t>
+          <t>Investment properties 3 $</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>-546.081</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>486.104</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>425.884</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>969.275</v>
+      <c r="E23" s="5" t="n">
+        <v>11988.347</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>11149.13</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Loss on sale of real estate assets, net of related costs 3</t>
+          <t>Debt 8 $</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="5" t="n">
+        <v>6375.86</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>6368.316</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
-        <v>7.247</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>11.154</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>2.254</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fair value adjustment on financial instruments 16</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-38.349</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>-30.555</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>8.452</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>17.498</v>
+          <t>Deferred tax liability 21</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>409.381</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>348.755</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Unit-based compensation expense 13(b)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>6.765</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>3.906</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>9.914</v>
+          <t>Accounts payable and accrued liabilities 10</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>281.595</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>369.186</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Subsequent events 24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 24</t>
+          <t>Subsequent events 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="5" t="n">
+        <v>14483.342</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>13355.444</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -5773,11 +5257,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n">
-        <v>-60.675</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>-184.269</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -5788,15 +5276,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Change in other non-cash operating items 17</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -5807,17 +5299,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n">
-        <v>-24.897</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>-12.161</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I28" s="5" t="n">
-        <v>2.686</v>
+        <v>-119.714</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-63.582</v>
+        <v>-791.564</v>
       </c>
     </row>
     <row r="29">
@@ -5828,12 +5324,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Items not affecting cash total</t>
+          <t>Finance cost - operations 16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -5848,16 +5344,16 @@
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>255.054</v>
+        <v>220.262</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>294.625</v>
+        <v>218.152</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>274.07</v>
+        <v>246.829</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>188.43</v>
+        <v>205.551</v>
       </c>
     </row>
     <row r="30">
@@ -5868,15 +5364,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Properties under development</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Acquisitions 3, 17</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -5887,21 +5387,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G30" s="5" t="n">
+        <v>-171.242</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-18.666</v>
+        <v>-169.726</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-104.468</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-152.813</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>-157.66</v>
       </c>
     </row>
     <row r="31">
@@ -5912,12 +5408,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Properties under development</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Additions 3, 17</t>
+          <t>Rental income accrued from the Bow and 100 Wynford 10</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -5932,16 +5428,16 @@
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-70.024</v>
+        <v>-86.55500000000001</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>-162.273</v>
+        <v>-92.92</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>-159.57</v>
+        <v>-93.736</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>-34.688</v>
+        <v>-94.559</v>
       </c>
     </row>
     <row r="32">
@@ -5952,12 +5448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Properties under development</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Net proceeds on disposition of properties under development</t>
+          <t>Net (income) loss from equity accounted investments 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -5982,12 +5478,10 @@
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>22.089</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.477</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>271.064</v>
       </c>
     </row>
     <row r="33">
@@ -5998,12 +5492,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Net proceeds on disposition of investment properties</t>
+          <t>Rent amortization of tenant inducements 15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -6017,19 +5511,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G33" s="5" t="n">
+        <v>4.691</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>371.9</v>
+        <v>4.514</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>330.94</v>
+        <v>4.574</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>101.948</v>
+        <v>4.508</v>
       </c>
     </row>
     <row r="34">
@@ -6040,12 +5532,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Redevelopment 3</t>
+          <t>Fair value adjustment on real estate assets 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -6059,19 +5551,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G34" s="5" t="n">
+        <v>-546.081</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>-7.203</v>
+        <v>486.104</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-22.403</v>
+        <v>425.884</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-19.323</v>
+        <v>969.275</v>
       </c>
     </row>
     <row r="35">
@@ -6082,19 +5572,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Capital expenditures 3</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CapitalExpenditure</t>
-        </is>
-      </c>
+          <t>Loss on sale of real estate assets, net of related costs 3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -6105,17 +5591,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>-35.582</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-41.168</v>
+        <v>7.247</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-39.588</v>
+        <v>11.154</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-41.995</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="36">
@@ -6126,12 +5614,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Leasing expenses and tenant inducements 3</t>
+          <t>Fair value adjustment on financial instruments 16</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -6146,16 +5634,16 @@
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-8.516</v>
+        <v>-38.349</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>-4.747</v>
+        <v>-30.555</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>-6.629</v>
+        <v>8.452</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-1.938</v>
+        <v>17.498</v>
       </c>
     </row>
     <row r="37">
@@ -6166,12 +5654,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Contributions to equity accounted investments</t>
+          <t>Unit-based compensation expense 13(b)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -6185,19 +5673,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G37" s="5" t="n">
+        <v>6.765</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>-36.988</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>-25.432</v>
+        <v>3.906</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-30.146</v>
+        <v>9.914</v>
       </c>
     </row>
     <row r="38">
@@ -6208,15 +5694,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Distributions received from equity accounted investments</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Deferred income tax recovery 24</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -6232,14 +5722,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H38" s="5" t="n">
-        <v>44.398</v>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I38" s="5" t="n">
-        <v>49.738</v>
+        <v>-60.675</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>49.511</v>
+        <v>-184.269</v>
       </c>
     </row>
     <row r="39">
@@ -6250,12 +5742,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Advances of mortgages receivable 6</t>
+          <t>Change in other non-cash operating items 17</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -6269,19 +5761,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G39" s="5" t="n">
+        <v>-24.897</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>-16.008</v>
+        <v>-12.161</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>-36.004</v>
+        <v>2.686</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-102.398</v>
+        <v>-63.582</v>
       </c>
     </row>
     <row r="40">
@@ -6292,12 +5782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Repayments of mortgages receivable 6</t>
+          <t>Items not affecting cash total</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -6311,19 +5801,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G40" s="5" t="n">
+        <v>255.054</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>52.864</v>
+        <v>294.625</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>80.64100000000001</v>
+        <v>274.07</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>17.045</v>
+        <v>188.43</v>
       </c>
     </row>
     <row r="41">
@@ -6334,12 +5822,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Properties under development</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Restricted cash 6</t>
+          <t>Acquisitions 3, 17</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -6353,17 +5841,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>-17.909</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>-69.181</v>
+        <v>-18.666</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>83.83799999999999</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>2.799</v>
+        <v>-104.468</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -6374,12 +5866,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Properties under development</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Investment properties total</t>
+          <t>Additions 3, 17</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -6394,16 +5886,16 @@
         </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>225.954</v>
+        <v>-70.024</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>112.862</v>
+        <v>-162.273</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>173.152</v>
+        <v>-159.57</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-59.185</v>
+        <v>-34.688</v>
       </c>
     </row>
     <row r="43">
@@ -6414,12 +5906,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Properties under development</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lines of credit 8</t>
+          <t>Net proceeds on disposition of properties under development</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -6438,14 +5930,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H43" s="5" t="n">
-        <v>292.21</v>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="5" t="n">
-        <v>31.444</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>538.213</v>
+        <v>22.089</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -6456,12 +5952,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Advances 8</t>
+          <t>Net proceeds on disposition of investment properties</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -6480,16 +5976,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H44" s="5" t="n">
+        <v>371.9</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>2.283</v>
+        <v>330.94</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>0.824</v>
+        <v>101.948</v>
       </c>
     </row>
     <row r="45">
@@ -6500,12 +5994,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Principal repayments 8</t>
+          <t>Redevelopment 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -6519,17 +6013,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n">
-        <v>-301.132</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>-144.534</v>
+        <v>-7.203</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>-160.146</v>
+        <v>-22.403</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>-127.545</v>
+        <v>-19.323</v>
       </c>
     </row>
     <row r="46">
@@ -6540,15 +6036,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redemption of debentures payable 8</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Capital expenditures 3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -6559,19 +6059,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G46" s="5" t="n">
+        <v>-35.582</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>-250</v>
+        <v>-41.168</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>-350</v>
+        <v>-39.588</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-400</v>
+        <v>-41.995</v>
       </c>
     </row>
     <row r="47">
@@ -6582,12 +6080,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of debentures payable, net 8</t>
+          <t>Leasing expenses and tenant inducements 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -6601,23 +6099,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G47" s="5" t="n">
+        <v>-8.516</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-4.747</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>248.8</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.629</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>-1.938</v>
       </c>
     </row>
     <row r="48">
@@ -6628,12 +6120,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cash distributions paid to unitholders 17</t>
+          <t>Contributions to equity accounted investments</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -6653,13 +6145,13 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>-170.564</v>
+        <v>-36.988</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>-183.36</v>
+        <v>-25.432</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-188.954</v>
+        <v>-30.146</v>
       </c>
     </row>
     <row r="49">
@@ -6670,12 +6162,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mortgages payable total</t>
+          <t>Distributions received from equity accounted investments</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -6689,17 +6181,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n">
-        <v>-528.2619999999999</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>-420.263</v>
+        <v>44.398</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>-410.979</v>
+        <v>49.738</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-177.462</v>
+        <v>49.511</v>
       </c>
     </row>
     <row r="50">
@@ -6710,19 +6204,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Advances of mortgages receivable 6</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -6739,13 +6229,13 @@
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>-12.776</v>
+        <v>-16.008</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>36.243</v>
+        <v>-36.004</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-48.217</v>
+        <v>-102.398</v>
       </c>
     </row>
     <row r="51">
@@ -6756,19 +6246,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year 7</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Repayments of mortgages receivable 6</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -6779,17 +6265,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n">
-        <v>124.141</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>76.887</v>
+        <v>52.864</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>64.111</v>
+        <v>80.64100000000001</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>100.354</v>
+        <v>17.045</v>
       </c>
     </row>
     <row r="52">
@@ -6800,19 +6288,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year 7</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Restricted cash 6</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -6824,16 +6308,16 @@
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>76.887</v>
+        <v>-17.909</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>64.111</v>
+        <v>-69.181</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>100.354</v>
+        <v>83.83799999999999</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>52.137</v>
+        <v>2.799</v>
       </c>
     </row>
     <row r="53">
@@ -6844,12 +6328,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Investment properties</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
+          <t>Investment properties total</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -6863,21 +6347,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G53" s="5" t="n">
+        <v>225.954</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>61.69</v>
+        <v>112.862</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>-119.714</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>173.152</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-59.185</v>
       </c>
     </row>
     <row r="54">
@@ -6888,12 +6368,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Net income from equity accounted investments 4</t>
+          <t>Lines of credit 8</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -6907,19 +6387,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
-        <v>-47.139</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>-145.459</v>
+        <v>292.21</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-2.477</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>31.444</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>538.213</v>
       </c>
     </row>
     <row r="55">
@@ -6930,12 +6410,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 22</t>
+          <t>Advances 8</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -6954,16 +6434,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H55" s="5" t="n">
-        <v>-32.345</v>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I55" s="5" t="n">
-        <v>-60.675</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.283</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.824</v>
       </c>
     </row>
     <row r="56">
@@ -6974,12 +6454,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Acquisitions 3</t>
+          <t>Principal repayments 8</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -6994,20 +6474,16 @@
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-78.44799999999999</v>
+        <v>-301.132</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>-0.066</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-144.534</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>-160.146</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>-127.545</v>
       </c>
     </row>
     <row r="57">
@@ -7018,12 +6494,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Unsecured term loans 8</t>
+          <t>Redemption of debentures payable 8</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -7037,21 +6513,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n">
-        <v>250</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>-125</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-250</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>-350</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-400</v>
       </c>
     </row>
     <row r="58">
@@ -7067,7 +6541,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New mortgages payable 8</t>
+          <t>Proceeds from issuance of debentures payable, net 8</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -7086,13 +6560,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H58" s="5" t="n">
-        <v>20.361</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>248.8</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -7113,7 +6587,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Net advances 8</t>
+          <t>Cash distributions paid to unitholders 17</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -7132,18 +6606,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H59" s="5" t="n">
+        <v>-170.564</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>2.283</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-183.36</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>-188.954</v>
       </c>
     </row>
     <row r="60">
@@ -7159,7 +6629,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of Units</t>
+          <t>Mortgages payable total</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -7173,23 +6643,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G60" s="5" t="n">
+        <v>-528.2619999999999</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-420.263</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>-410.979</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>-177.462</v>
       </c>
     </row>
     <row r="61">
@@ -7205,10 +6669,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Units repurchased and cancelled 13(d)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Increase (decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -7219,21 +6687,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G61" s="5" t="n">
-        <v>-297.056</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>-42.723</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-12.776</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>36.243</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>-48.217</v>
       </c>
     </row>
     <row r="62">
@@ -7244,17 +6710,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t>Cash and cash equivalents, beginning of year 7</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7268,20 +6734,16 @@
         </is>
       </c>
       <c r="G62" s="5" t="n">
-        <v>844.823</v>
+        <v>124.141</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>61.69</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>76.887</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>64.111</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>100.354</v>
       </c>
     </row>
     <row r="63">
@@ -7292,15 +6754,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>(Gain) loss on sale of real estate assets, net of related costs 3</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year 7</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -7312,20 +6778,16 @@
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-7.332</v>
+        <v>76.887</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>7.247</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>64.111</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>100.354</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>52.137</v>
       </c>
     </row>
     <row r="64">
@@ -7336,15 +6798,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery) 22</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Net income (loss)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -7355,16 +6821,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G64" s="5" t="n">
-        <v>100.108</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>-32.345</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>61.69</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>-119.714</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -7380,12 +6846,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Properties under development</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Acquisitions 3</t>
+          <t>Net income from equity accounted investments 4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -7400,15 +6866,13 @@
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-90.845</v>
+        <v>-47.139</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>-18.666</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-145.459</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>-2.477</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -7424,17 +6888,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Deferred revenue 10</t>
+          <t>Deferred income tax recovery 22</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ChangeInOtherWorkingCapital</t>
+          <t>DeferredTax</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7447,18 +6911,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G66" s="5" t="n">
-        <v>118.608</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>-32.345</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>-60.675</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -7479,7 +6941,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Net proceeds on disposition of real estate assets</t>
+          <t>Acquisitions 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -7494,10 +6956,10 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>263.679</v>
+        <v>-78.44799999999999</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>371.9</v>
+        <v>-0.066</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -7518,12 +6980,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Redevelopment, net of insurance proceeds 3</t>
+          <t>Unsecured term loans 8</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -7538,10 +7000,10 @@
         </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>5.425</v>
+        <v>250</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>-7.203</v>
+        <v>-125</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -7562,12 +7024,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Equity accounted investments, net</t>
+          <t>New mortgages payable 8</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -7581,11 +7043,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G69" s="5" t="n">
-        <v>57.559</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>7.41</v>
+        <v>20.361</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -7606,12 +7070,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mortgages receivable, net</t>
+          <t>Net advances 8</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -7625,16 +7089,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G70" s="5" t="n">
-        <v>32.732</v>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>36.856</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>2.283</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -7650,12 +7116,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Investment properties</t>
+          <t>Mortgages payable</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Proceeds from sale of Primaris REIT units</t>
+          <t>Proceeds from issuance of Units</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -7669,13 +7135,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n">
-        <v>49.275</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>-0.013</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -7701,7 +7167,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of Units 17</t>
+          <t>Units repurchased and cancelled 13(d)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -7716,10 +7182,10 @@
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.331</v>
+        <v>-297.056</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>-0.013</v>
+        <v>-42.723</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -7740,15 +7206,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Distributions paid to unitholders 17</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -7760,10 +7230,10 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-179.743</v>
+        <v>844.823</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>-170.564</v>
+        <v>61.69</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -7784,19 +7254,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mortgages payable</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Decrease in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>(Gain) loss on sale of real estate assets, net of related costs 3</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -7808,10 +7274,10 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-47.254</v>
+        <v>-7.332</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>-12.776</v>
+        <v>7.247</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -7827,16 +7293,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rentals from investment properties 15</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Deferred income tax expense (recovery) 22</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -7848,28 +7322,36 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>834.64</v>
+        <v>100.108</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>847.146</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>816.99</v>
-      </c>
-      <c r="J75" s="5" t="n">
-        <v>815.128</v>
+        <v>-32.345</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Properties under development</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Property operating costs</t>
+          <t>Acquisitions 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -7884,33 +7366,41 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-299.691</v>
+        <v>-90.845</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>-300.542</v>
-      </c>
-      <c r="I76" s="5" t="n">
-        <v>-297.072</v>
-      </c>
-      <c r="J76" s="5" t="n">
-        <v>-306.045</v>
+        <v>-18.666</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Investment properties</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Net operating income</t>
+          <t>Deferred revenue 10</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>ChangeInOtherWorkingCapital</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7924,28 +7414,38 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>534.949</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>546.604</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>519.918</v>
-      </c>
-      <c r="J77" s="5" t="n">
-        <v>509.083</v>
+        <v>118.608</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Investment properties</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Net income (loss) from equity accounted investments 4</t>
+          <t>Net proceeds on disposition of real estate assets</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -7959,33 +7459,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>2.477</v>
-      </c>
-      <c r="J78" s="5" t="n">
-        <v>-271.064</v>
+      <c r="G78" s="5" t="n">
+        <v>263.679</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Investment properties</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Finance cost - operations 16</t>
+          <t>Redevelopment, net of insurance proceeds 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -8000,35 +7504,39 @@
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-220.262</v>
+        <v>5.425</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>-218.152</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>-246.829</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>-205.551</v>
+        <v>-7.203</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Investment properties</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Finance income 16</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Equity accounted investments, net</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -8040,28 +7548,36 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>14.793</v>
+        <v>57.559</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>13.849</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>11.577</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>14.498</v>
+        <v>7.41</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Investment properties</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Trust expenses, net</t>
+          <t>Mortgages receivable, net</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -8075,33 +7591,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>-20.58</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>-19.381</v>
+      <c r="G81" s="5" t="n">
+        <v>32.732</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>36.856</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Investment properties</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fair value adjustment on financial instruments 16</t>
+          <t>Proceeds from sale of Primaris REIT units</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -8116,28 +7636,38 @@
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>38.349</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>30.555</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>-8.452</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>-17.498</v>
+        <v>49.275</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Mortgages payable</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fair value adjustment on real estate assets 3</t>
+          <t>Proceeds from issuance of Units 17</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -8152,28 +7682,36 @@
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>546.081</v>
+        <v>-0.331</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>-486.104</v>
-      </c>
-      <c r="I83" s="5" t="n">
-        <v>-425.884</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>-969.275</v>
+        <v>-0.013</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Mortgages payable</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Loss on sale of real estate assets, net of related costs 3</t>
+          <t>Distributions paid to unitholders 17</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -8187,34 +7725,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G84" s="5" t="n">
+        <v>-179.743</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>-7.247</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>-11.154</v>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>-2.254</v>
+        <v>-170.564</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Mortgages payable</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Transaction costs 18</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Decrease in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -8225,23 +7773,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G85" s="5" t="n">
+        <v>-47.254</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>-12.776</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J85" s="5" t="n">
-        <v>-12.74</v>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -8253,14 +7799,10 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Net loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Rentals from investment properties 15</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -8271,21 +7813,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G86" s="5" t="n">
+        <v>834.64</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>847.146</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-178.927</v>
+        <v>816.99</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-974.182</v>
+        <v>815.128</v>
       </c>
     </row>
     <row r="87">
@@ -8297,7 +7835,7 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Income tax recovery 24</t>
+          <t>Property operating costs</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -8311,21 +7849,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G87" s="5" t="n">
+        <v>-299.691</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>-300.542</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>59.213</v>
+        <v>-297.072</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>182.618</v>
+        <v>-306.045</v>
       </c>
     </row>
     <row r="88">
@@ -8337,12 +7871,12 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Net operating income</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8355,21 +7889,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G88" s="5" t="n">
+        <v>534.949</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>546.604</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>-119.714</v>
+        <v>519.918</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>-791.564</v>
+        <v>509.083</v>
       </c>
     </row>
     <row r="89">
@@ -8378,14 +7908,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Other comprehensive income (loss)</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Items that are or may be reclassified subsequently to net loss 14</t>
+          <t>Net income (loss) from equity accounted investments 4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -8410,10 +7936,10 @@
         </is>
       </c>
       <c r="I89" s="5" t="n">
-        <v>393.292</v>
+        <v>2.477</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>-219.573</v>
+        <v>-271.064</v>
       </c>
     </row>
     <row r="90">
@@ -8422,14 +7948,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Other comprehensive income (loss)</t>
-        </is>
-      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Total comprehensive income (loss) attributable to unitholders</t>
+          <t>Finance cost - operations 16</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -8444,16 +7966,16 @@
         </is>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1166.393</v>
+        <v>-220.262</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>-69.512</v>
+        <v>-218.152</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>273.578</v>
+        <v>-246.829</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>-1011.137</v>
+        <v>-205.551</v>
       </c>
     </row>
     <row r="91">
@@ -8462,17 +7984,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Unitholders' equity, January 1, 2024 $5,219,408 $6,778,212 ($7,131,874)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Finance income 16</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -8483,21 +8005,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G91" s="5" t="n">
+        <v>14.793</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>13.849</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>5192.375</v>
+        <v>11.577</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>326.629</v>
+        <v>14.498</v>
       </c>
     </row>
     <row r="92">
@@ -8506,14 +8024,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Issuance of Units 1,413 — —</t>
+          <t>Trust expenses, net</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -8532,16 +8046,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H92" s="5" t="n">
-        <v>1.413</v>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I92" s="5" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-20.58</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>-19.381</v>
       </c>
     </row>
     <row r="93">
@@ -8550,14 +8064,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Net loss — (119,714) —</t>
+          <t>Fair value adjustment on financial instruments 16</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -8571,21 +8081,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" s="5" t="n">
+        <v>38.349</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>-119.714</v>
+        <v>30.555</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>-119.714</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.452</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>-17.498</v>
       </c>
     </row>
     <row r="94">
@@ -8594,14 +8100,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Distributions to unitholders 13 — — (188,623)</t>
+          <t>Fair value adjustment on real estate assets 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -8615,21 +8117,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G94" s="5" t="n">
+        <v>546.081</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>-188.623</v>
+        <v>-486.104</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-188.623</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-425.884</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>-969.275</v>
       </c>
     </row>
     <row r="95">
@@ -8638,14 +8136,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Distributions in Units 13 157,209 — (157,209)</t>
+          <t>Loss on sale of real estate assets, net of related costs 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -8664,20 +8158,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H95" s="5" t="n">
+        <v>-7.247</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>-11.154</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>-2.254</v>
       </c>
     </row>
     <row r="96">
@@ -8686,14 +8174,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Other comprehensive income — — —</t>
+          <t>Transaction costs 18</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -8717,11 +8201,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="5" t="n">
-        <v>393.292</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="5" t="n">
-        <v>393.292</v>
+        <v>-12.74</v>
       </c>
     </row>
     <row r="97">
@@ -8730,17 +8216,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2024 5,378,030 6,658,498 (7,477,706)</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Net loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -8762,10 +8248,10 @@
         </is>
       </c>
       <c r="I97" s="5" t="n">
-        <v>5278.743</v>
+        <v>-178.927</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>719.921</v>
+        <v>-974.182</v>
       </c>
     </row>
     <row r="98">
@@ -8774,17 +8260,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Issuance of Units 25,751 — —</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>Income tax recovery 24</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -8806,12 +8292,10 @@
         </is>
       </c>
       <c r="I98" s="5" t="n">
-        <v>25.751</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>59.213</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>182.618</v>
       </c>
     </row>
     <row r="99">
@@ -8820,17 +8304,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Net loss — (791,564) —</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -8852,12 +8336,10 @@
         </is>
       </c>
       <c r="I99" s="5" t="n">
+        <v>-119.714</v>
+      </c>
+      <c r="J99" s="5" t="n">
         <v>-791.564</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="100">
@@ -8868,12 +8350,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Distributions to unitholders 13 — — (157,639)</t>
+          <t>Items that are or may be reclassified subsequently to net loss 14</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -8898,12 +8380,10 @@
         </is>
       </c>
       <c r="I100" s="5" t="n">
-        <v>-157.639</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>393.292</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>-219.573</v>
       </c>
     </row>
     <row r="101">
@@ -8914,12 +8394,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Distributions in Units 13 39,684 — (39,684)</t>
+          <t>Total comprehensive income (loss) attributable to unitholders</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -8933,25 +8413,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" s="5" t="n">
+        <v>1166.393</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>-69.512</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>273.578</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>-1011.137</v>
       </c>
     </row>
     <row r="102">
@@ -8967,7 +8439,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Other comprehensive loss 14 — — —</t>
+          <t>Unitholders' equity, January 1, 2024 $5,219,408 $6,778,212 ($7,131,874)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8981,17 +8453,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G102" s="5" t="n">
-        <v>-131.202</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>-131.202</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-219.573</v>
+        <v>5192.375</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-219.573</v>
+        <v>326.629</v>
       </c>
     </row>
     <row r="103">
@@ -9007,7 +8483,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2025 5,443,465 5,866,934 (7,675,029)</t>
+          <t>Issuance of Units 1,413 — —</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -9026,16 +8502,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H103" s="5" t="n">
+        <v>1.413</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>4135.718</v>
-      </c>
-      <c r="J103" s="5" t="n">
-        <v>500.348</v>
+        <v>1.413</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -9044,10 +8520,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Net income from equity accounted investments 4</t>
+          <t>Net loss — (119,714) —</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -9061,14 +8541,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G104" s="5" t="n">
-        <v>47.139</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>145.459</v>
+        <v>-119.714</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>2.477</v>
+        <v>-119.714</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -9082,10 +8564,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gain on disposal of purchase option</t>
+          <t>Distributions to unitholders 13 — — (188,623)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -9105,12 +8591,10 @@
         </is>
       </c>
       <c r="H105" s="5" t="n">
-        <v>30.568</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-188.623</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>-188.623</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -9124,10 +8608,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Trust expenses</t>
+          <t>Distributions in Units 13 157,209 — (157,209)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -9141,14 +8629,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G106" s="5" t="n">
-        <v>-22.121</v>
-      </c>
-      <c r="H106" s="5" t="n">
-        <v>-24.385</v>
-      </c>
-      <c r="I106" s="5" t="n">
-        <v>-20.58</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -9162,17 +8656,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Net income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Other comprehensive income — — —</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -9188,16 +8682,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H107" s="5" t="n">
-        <v>31.147</v>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I107" s="5" t="n">
-        <v>-178.927</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>393.292</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>393.292</v>
       </c>
     </row>
     <row r="108">
@@ -9206,10 +8700,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Income tax recovery 22</t>
+          <t>Unitholders' equity, December 31, 2024 5,378,030 6,658,498 (7,477,706)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -9228,16 +8726,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H108" s="5" t="n">
-        <v>30.543</v>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I108" s="5" t="n">
-        <v>59.213</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5278.743</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>719.921</v>
       </c>
     </row>
     <row r="109">
@@ -9246,17 +8744,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Issuance of Units 25,751 — —</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -9272,11 +8770,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H109" s="5" t="n">
-        <v>61.69</v>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I109" s="5" t="n">
-        <v>-119.714</v>
+        <v>25.751</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -9292,19 +8792,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Items that are or may be reclassified subsequently to net income (loss) 14</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Net loss — (791,564) —</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -9320,11 +8816,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H110" s="5" t="n">
-        <v>-131.202</v>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I110" s="5" t="n">
-        <v>393.292</v>
+        <v>-791.564</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -9345,7 +8843,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Unitholders' equity, January 1, 2023 $5,124,265 $6,716,522 ($6,811,331)</t>
+          <t>Distributions to unitholders 13 — — (157,639)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -9364,11 +8862,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H111" s="5" t="n">
-        <v>5487.287</v>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I111" s="5" t="n">
-        <v>457.831</v>
+        <v>-157.639</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -9389,7 +8889,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Issuance of Units 1,695 — —</t>
+          <t>Distributions in Units 13 39,684 — (39,684)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -9408,8 +8908,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H112" s="5" t="n">
-        <v>1.695</v>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -9435,7 +8937,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Net income — 61,690 —</t>
+          <t>Other comprehensive loss 14 — — —</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -9450,20 +8952,16 @@
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>61.69</v>
+        <v>-131.202</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>61.69</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-131.202</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>-219.573</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>-219.573</v>
       </c>
     </row>
     <row r="114">
@@ -9479,7 +8977,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Distributions to unitholders 13 — — (184,372)</t>
+          <t>Unitholders' equity, December 31, 2025 5,443,465 5,866,934 (7,675,029)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -9498,18 +8996,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H114" s="5" t="n">
-        <v>-184.372</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>4135.718</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>500.348</v>
       </c>
     </row>
     <row r="115">
@@ -9518,14 +9014,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Distributions in Units 13 136,171 — (136,171)</t>
+          <t>Net income from equity accounted investments 4</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9539,20 +9031,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G115" s="5" t="n">
+        <v>47.139</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>145.459</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>2.477</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -9566,14 +9052,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Units repurchased and cancelled 13(d) (42,723) — —</t>
+          <t>Gain on disposal of purchase option</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9587,11 +9069,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G116" s="5" t="n">
-        <v>-42.723</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>-42.723</v>
+        <v>30.568</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -9610,14 +9094,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2023 5,219,408 6,778,212 (7,131,874)</t>
+          <t>Trust expenses</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9631,16 +9111,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G117" s="5" t="n">
+        <v>-22.121</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>5192.375</v>
+        <v>-24.385</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>326.629</v>
+        <v>-20.58</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -9654,17 +9132,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Other comprehensive income 14 — — —</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
+          <t>Net income (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -9675,14 +9153,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G118" s="5" t="n">
-        <v>321.57</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>393.292</v>
+        <v>31.147</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>393.292</v>
+        <v>-178.927</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -9696,17 +9176,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2024 $5,378,030 $6,658,498 ($7,477,706)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>Income tax recovery 22</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -9723,10 +9203,10 @@
         </is>
       </c>
       <c r="H119" s="5" t="n">
-        <v>5278.743</v>
+        <v>30.543</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>719.921</v>
+        <v>59.213</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -9743,10 +9223,14 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Proceeds on disposal of purchase option 6</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>Net income (loss)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -9763,12 +9247,10 @@
         </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>30.568</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>61.69</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>-119.714</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -9782,13 +9264,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of real estate assets, net of related costs 3</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>Items that are or may be reclassified subsequently to net income (loss) 14</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -9799,16 +9289,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G121" s="5" t="n">
-        <v>7.332</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H121" s="5" t="n">
-        <v>-7.247</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-131.202</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>393.292</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -9822,17 +9312,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Net income before income taxes</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Unitholders' equity, January 1, 2023 $5,124,265 $6,716,522 ($6,811,331)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -9843,16 +9333,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G122" s="5" t="n">
-        <v>946.26</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>31.147</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5487.287</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>457.831</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -9866,10 +9356,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense) 22</t>
+          <t>Issuance of Units 1,695 — —</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9883,11 +9377,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G123" s="5" t="n">
-        <v>-101.437</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H123" s="5" t="n">
-        <v>30.543</v>
+        <v>1.695</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -9906,17 +9402,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Net income — 61,690 —</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -9928,7 +9424,7 @@
         </is>
       </c>
       <c r="G124" s="5" t="n">
-        <v>844.823</v>
+        <v>61.69</v>
       </c>
       <c r="H124" s="5" t="n">
         <v>61.69</v>
@@ -9952,12 +9448,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Items that are or may be reclassified subsequently to net income 14</t>
+          <t>Distributions to unitholders 13 — — (184,372)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9971,11 +9467,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G125" s="5" t="n">
-        <v>321.57</v>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>-131.202</v>
+        <v>-184.372</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10001,7 +9499,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Unitholders' equity, January 1, 2022 $5,417,419 $5,871,699 ($6,651,546)</t>
+          <t>Distributions in Units 13 136,171 — (136,171)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -10015,11 +9513,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G126" s="5" t="n">
-        <v>4773.833</v>
-      </c>
-      <c r="H126" s="5" t="n">
-        <v>136.261</v>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -10045,7 +9547,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of Units 3,902 — —</t>
+          <t>Units repurchased and cancelled 13(d) (42,723) — —</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -10060,12 +9562,10 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>3.902</v>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-42.723</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>-42.723</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -10091,7 +9591,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Net income — 844,823 —</t>
+          <t>Unitholders' equity, December 31, 2023 5,219,408 6,778,212 (7,131,874)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -10105,18 +9605,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G128" s="5" t="n">
-        <v>844.823</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>5192.375</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>326.629</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -10137,7 +9635,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Distributions to unitholders — — (159,785)</t>
+          <t>Other comprehensive income 14 — — —</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -10152,17 +9650,13 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>-159.785</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>321.57</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>393.292</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>393.292</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -10183,7 +9677,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Units repurchased and cancelled 13(d) (297,056) — —</t>
+          <t>Unitholders' equity, December 31, 2024 $5,378,030 $6,658,498 ($7,477,706)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -10197,18 +9691,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G130" s="5" t="n">
-        <v>-297.056</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>5278.743</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>719.921</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -10222,14 +9714,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2022 5,124,265 6,716,522 (6,811,331)</t>
+          <t>Proceeds on disposal of purchase option 6</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -10243,11 +9731,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G131" s="5" t="n">
-        <v>5487.287</v>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H131" s="5" t="n">
-        <v>457.831</v>
+        <v>30.568</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -10266,14 +9756,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of Units 1,695 — —</t>
+          <t>Gain (loss) on sale of real estate assets, net of related costs 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -10288,12 +9774,10 @@
         </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.332</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>-7.247</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -10312,17 +9796,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Distributions to unitholders — — (184,372)</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>Net income before income taxes</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -10334,12 +9818,10 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>-184.372</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>946.26</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>31.147</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -10358,17 +9840,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Value of   Accumulated   Accumulated  comprehensive</t>
-        </is>
-      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2023 $5,083,237 $6,778,212 ($6,995,703)</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Income tax recovery (expense) 22</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -10380,10 +9862,10 @@
         </is>
       </c>
       <c r="G134" s="5" t="n">
-        <v>5192.375</v>
+        <v>-101.437</v>
       </c>
       <c r="H134" s="5" t="n">
-        <v>326.629</v>
+        <v>30.543</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -10402,32 +9884,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Property operating income</t>
-        </is>
-      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Rentals from investment properties 14 $</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" s="5" t="n">
-        <v>1149.45</v>
-      </c>
-      <c r="F135" s="5" t="n">
-        <v>1098.68</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>844.823</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>61.69</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -10448,30 +9930,30 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Property operating costs</t>
+          <t>Items that are or may be reclassified subsequently to net income 14</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" s="5" t="n">
-        <v>-438.475</v>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>-435.014</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>-131.202</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -10492,30 +9974,30 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Property operating income total</t>
+          <t>Unitholders' equity, January 1, 2022 $5,417,419 $5,871,699 ($6,651,546)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" s="5" t="n">
-        <v>710.975</v>
-      </c>
-      <c r="F137" s="5" t="n">
-        <v>663.6660000000001</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>4773.833</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>136.261</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -10536,25 +10018,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Net income (loss) from equity accounted investments 4</t>
+          <t>Proceeds from issuance of Units 3,902 — —</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" s="5" t="n">
-        <v>31.201</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>-16.986</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>3.902</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -10580,25 +10064,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Finance cost - operations 15</t>
+          <t>Net income — 844,823 —</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" s="5" t="n">
-        <v>-256.496</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>-228.869</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>844.823</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -10624,29 +10110,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Finance income 15</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="n">
-        <v>15.036</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>33.399</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Distributions to unitholders — — (159,785)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>-159.785</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -10672,25 +10156,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Trust expenses</t>
+          <t>Units repurchased and cancelled 13(d) (297,056) — —</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" s="5" t="n">
-        <v>-27.293</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>-14.297</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>-297.056</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -10716,30 +10202,30 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fair value adjustment on financial instruments 15</t>
+          <t>Unitholders' equity, December 31, 2022 5,124,265 6,716,522 (6,811,331)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" s="5" t="n">
-        <v>-19.483</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>82.974</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>5487.287</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>457.831</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -10760,25 +10246,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Fair value adjustment on real estate assets 3</t>
+          <t>Proceeds from issuance of Units 1,695 — —</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" s="5" t="n">
-        <v>-103.903</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>-1195.958</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>1.695</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -10804,25 +10292,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of real estate assets, net of related costs 3</t>
+          <t>Distributions to unitholders — — (184,372)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" s="5" t="n">
-        <v>25.632</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>-2.229</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>-184.372</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -10848,34 +10338,30 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Property operating income</t>
+          <t>Value of   Accumulated   Accumulated  comprehensive</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Net income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="n">
-        <v>375.669</v>
-      </c>
-      <c r="F145" s="5" t="n">
-        <v>-678.3</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Unitholders' equity, December 31, 2023 $5,083,237 $6,778,212 ($6,995,703)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>5192.375</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>326.629</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -10901,19 +10387,15 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Income tax (expense) recovery 21</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Rentals from investment properties 14 $</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" s="5" t="n">
-        <v>-35.38</v>
+        <v>1149.45</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>53.741</v>
+        <v>1098.68</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -10949,19 +10431,15 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Property operating costs</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" s="5" t="n">
-        <v>340.289</v>
+        <v>-438.475</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>-624.559</v>
+        <v>-435.014</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -10992,24 +10470,20 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Items that are or may be reclassified subsequently to net income (loss) 13</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Property operating income total</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" s="5" t="n">
-        <v>-125.326</v>
+        <v>710.975</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>-86.66200000000001</v>
+        <v>663.6660000000001</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -11040,20 +10514,20 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Total comprehensive income (loss) attributable to unitholders $</t>
+          <t>Net income (loss) from equity accounted investments 4</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" s="5" t="n">
-        <v>214.963</v>
+        <v>31.201</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>-711.221</v>
+        <v>-16.986</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -11084,20 +10558,20 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Unitholders' equity, January 1, 2019 $ 5,366,464 $ 5,558,062 $ (4,096,250) $</t>
+          <t>Finance cost - operations 15</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" s="5" t="n">
-        <v>7200.1</v>
+        <v>-256.496</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>371.824</v>
+        <v>-228.869</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -11128,22 +10602,24 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of Units 23,035 - -</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>Finance income 15</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E151" s="5" t="n">
-        <v>23.035</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15.036</v>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>33.399</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -11174,22 +10650,20 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Net income - 340,289 -</t>
+          <t>Trust expenses</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" s="5" t="n">
-        <v>340.289</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-27.293</v>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>-14.297</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -11220,22 +10694,20 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Distributions to unitholders - - (394,181)</t>
+          <t>Fair value adjustment on financial instruments 15</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" s="5" t="n">
-        <v>-394.181</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-19.483</v>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>82.974</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -11266,20 +10738,20 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Other comprehensive loss 13 - - -</t>
+          <t>Fair value adjustment on real estate assets 3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" s="5" t="n">
-        <v>-125.326</v>
+        <v>-103.903</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>-125.326</v>
+        <v>-1195.958</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -11310,20 +10782,20 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Unitholders' equity, December 31, 2019 5,389,499 5,898,351 (4,490,431)</t>
+          <t>Gain (loss) on sale of real estate assets, net of related costs 3</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" s="5" t="n">
-        <v>7043.917</v>
+        <v>25.632</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>246.498</v>
+        <v>-2.229</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -11354,22 +10826,24 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of Units 2,267 - -</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>Net income (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
-        <v>2.267</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>375.669</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>-678.3</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -11400,22 +10874,24 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Net loss - (624,559) -</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Income tax (expense) recovery 21</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E157" s="5" t="n">
-        <v>-624.559</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-35.38</v>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>53.741</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -11446,22 +10922,24 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Value of Accumulated Accumulated comprehensive</t>
+          <t>Property operating income</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Distributions to unitholders - - (263,572)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>Net income (loss)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="n">
-        <v>-263.572</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>340.289</v>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>-624.559</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -11492,37 +10970,537 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Items that are or may be reclassified subsequently to net income (loss) 13</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="n">
+        <v>-125.326</v>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>-86.66200000000001</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Total comprehensive income (loss) attributable to unitholders $</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" s="5" t="n">
+        <v>214.963</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>-711.221</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
           <t>Value of Accumulated Accumulated comprehensive</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, January 1, 2019 $ 5,366,464 $ 5,558,062 $ (4,096,250) $</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" s="5" t="n">
+        <v>7200.1</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>371.824</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of Units 23,035 - -</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" s="5" t="n">
+        <v>23.035</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Net income - 340,289 -</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" s="5" t="n">
+        <v>340.289</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders - - (394,181)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" s="5" t="n">
+        <v>-394.181</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss 13 - - -</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" s="5" t="n">
+        <v>-125.326</v>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>-125.326</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Unitholders' equity, December 31, 2019 5,389,499 5,898,351 (4,490,431)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" s="5" t="n">
+        <v>7043.917</v>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>246.498</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of Units 2,267 - -</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" s="5" t="n">
+        <v>2.267</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Net loss - (624,559) -</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" s="5" t="n">
+        <v>-624.559</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders - - (263,572)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" s="5" t="n">
+        <v>-263.572</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Value of Accumulated Accumulated comprehensive</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
         <is>
           <t>Unitholders' equity, December 31, 2020 $ 5,391,766 $ 5,273,792 $ (4,754,003) $</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" s="5" t="n">
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" s="5" t="n">
         <v>6071.391</v>
       </c>
-      <c r="F159" s="5" t="n">
+      <c r="F170" s="5" t="n">
         <v>159.836</v>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
         <is>
           <t>-</t>
         </is>
